--- a/branch details.xlsx
+++ b/branch details.xlsx
@@ -13,9 +13,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1611</definedName>
   </definedNames>
   <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 
@@ -71850,10 +71847,7 @@
       <c r="K1612" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1611">
-    <filterColumn colId="3"/>
-    <filterColumn colId="10"/>
-  </autoFilter>
+  <autoFilter ref="A1:K1611"/>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
